--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2024_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -954,19 +954,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.72</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.43</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="22">
@@ -977,19 +977,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.16</v>
+        <v>0.79</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23">
@@ -1000,19 +1000,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.01</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>
